--- a/parquet - schema/TemplateType.xlsx
+++ b/parquet - schema/TemplateType.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +600,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Capital Assets Schedule</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CAPITAL_ASSETS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tax Base Schedule</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TAX_BASE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Issuer Overview</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OVERVIEW</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pension Disclosures</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OPEB Disclosures</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>OPEB</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FAQS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
